--- a/artfynd/A 24268-2021 artfynd.xlsx
+++ b/artfynd/A 24268-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24268-2021 artfynd.xlsx
+++ b/artfynd/A 24268-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1681,6 +1681,118 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124748679</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Hullsjöbodarna, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>588185</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6933062</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24268-2021 artfynd.xlsx
+++ b/artfynd/A 24268-2021 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>124748679</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
